--- a/Model_Statistics.xlsx
+++ b/Model_Statistics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Communication Services_w</t>
+          <t>Basic Materials_w</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -462,1204 +462,1204 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8305066699583711</v>
+        <v>0.6253137242539155</v>
       </c>
       <c r="D2" t="n">
-        <v>4.229574059987625e-07</v>
+        <v>0.0007716825938648</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Communication Services_w</t>
+          <t>Basic Materials_w</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Communication Services_logp</t>
+          <t>Basic Materials_logp</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8305066699583711</v>
+        <v>0.6253137242539155</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000400193454887</v>
+        <v>0.6315581584068093</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Communication Services_w</t>
+          <t>Basic Materials_w</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical_logp</t>
+          <t>Communication Services_logp</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8305066699583711</v>
+        <v>0.6253137242539155</v>
       </c>
       <c r="D4" t="n">
-        <v>0.035265436455887</v>
+        <v>0.2670570299462874</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Communication Services_w</t>
+          <t>Basic Materials_w</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Consumer Defensive_logp</t>
+          <t>Consumer Cyclical_logp</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8305066699583711</v>
+        <v>0.6253137242539155</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3279081568833426</v>
+        <v>0.220467125630697</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Communication Services_w</t>
+          <t>Basic Materials_w</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Energy_logp</t>
+          <t>Consumer Defensive_logp</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8305066699583711</v>
+        <v>0.6253137242539155</v>
       </c>
       <c r="D6" t="n">
-        <v>0.215209795880392</v>
+        <v>0.5141808647353356</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Communication Services_w</t>
+          <t>Basic Materials_w</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Financial Services_logp</t>
+          <t>Energy_logp</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.8305066699583711</v>
+        <v>0.6253137242539155</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5016630632268477</v>
+        <v>0.5626489278183689</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Communication Services_w</t>
+          <t>Basic Materials_w</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Healthcare_logp</t>
+          <t>Financial Services_logp</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.8305066699583711</v>
+        <v>0.6253137242539155</v>
       </c>
       <c r="D8" t="n">
-        <v>2.133045637052378e-06</v>
+        <v>0.8648731568638514</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Communication Services_w</t>
+          <t>Basic Materials_w</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Industrials_logp</t>
+          <t>Healthcare_logp</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.8305066699583711</v>
+        <v>0.6253137242539155</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7738468672145808</v>
+        <v>0.5175423719647108</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Communication Services_w</t>
+          <t>Basic Materials_w</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Technology_logp</t>
+          <t>Industrials_logp</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.8305066699583711</v>
+        <v>0.6253137242539155</v>
       </c>
       <c r="D10" t="n">
-        <v>4.459421672218809e-18</v>
+        <v>0.0317681259200791</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Communication Services_w</t>
+          <t>Basic Materials_w</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Utilities_logp</t>
+          <t>Real Estate_logp</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8305066699583711</v>
+        <v>0.6253137242539155</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0330759614152962</v>
+        <v>0.2454635870986739</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Communication Services_w</t>
+          <t>Basic Materials_w</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>log_real_income</t>
+          <t>Technology_logp</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.8305066699583711</v>
+        <v>0.6253137242539155</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0039451251745853</v>
+        <v>1.343494401495488e-09</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Consumer Cyclical_w</t>
+          <t>Basic Materials_w</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>const</t>
+          <t>Utilities_logp</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.8696640014136835</v>
+        <v>0.6253137242539155</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0005505084370667</v>
+        <v>0.019437774141156</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Consumer Cyclical_w</t>
+          <t>Basic Materials_w</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Communication Services_logp</t>
+          <t>log_real_income</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.8696640014136835</v>
+        <v>0.6253137242539155</v>
       </c>
       <c r="D14" t="n">
-        <v>0.868647883567145</v>
+        <v>0.0298119834573396</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Consumer Cyclical_w</t>
+          <t>Communication Services_w</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Consumer Cyclical_logp</t>
+          <t>const</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.8696640014136835</v>
+        <v>0.7906570816031738</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0357363702381925</v>
+        <v>0.5318709061184873</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Consumer Cyclical_w</t>
+          <t>Communication Services_w</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Consumer Defensive_logp</t>
+          <t>Basic Materials_logp</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8696640014136835</v>
+        <v>0.7906570816031738</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4604933484063336</v>
+        <v>0.0007219181277303</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Consumer Cyclical_w</t>
+          <t>Communication Services_w</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Energy_logp</t>
+          <t>Communication Services_logp</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.8696640014136835</v>
+        <v>0.7906570816031738</v>
       </c>
       <c r="D17" t="n">
-        <v>1.450084769420352e-05</v>
+        <v>0.0176224758218555</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Consumer Cyclical_w</t>
+          <t>Communication Services_w</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Financial Services_logp</t>
+          <t>Consumer Cyclical_logp</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.8696640014136835</v>
+        <v>0.7906570816031738</v>
       </c>
       <c r="D18" t="n">
-        <v>0.009789415242860301</v>
+        <v>0.0006147510098906</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Consumer Cyclical_w</t>
+          <t>Communication Services_w</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Healthcare_logp</t>
+          <t>Consumer Defensive_logp</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.8696640014136835</v>
+        <v>0.7906570816031738</v>
       </c>
       <c r="D19" t="n">
-        <v>0.07084939221753379</v>
+        <v>0.5185842671152141</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Consumer Cyclical_w</t>
+          <t>Communication Services_w</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Industrials_logp</t>
+          <t>Energy_logp</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.8696640014136835</v>
+        <v>0.7906570816031738</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4777952324562176</v>
+        <v>0.07822811533681021</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Consumer Cyclical_w</t>
+          <t>Communication Services_w</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Technology_logp</t>
+          <t>Financial Services_logp</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.8696640014136835</v>
+        <v>0.7906570816031738</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8327365865595232</v>
+        <v>0.5229891953737279</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Consumer Cyclical_w</t>
+          <t>Communication Services_w</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Utilities_logp</t>
+          <t>Healthcare_logp</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.8696640014136835</v>
+        <v>0.7906570816031738</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0001151859771554</v>
+        <v>0.0006500291207483</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Consumer Cyclical_w</t>
+          <t>Communication Services_w</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>log_real_income</t>
+          <t>Industrials_logp</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.8696640014136835</v>
+        <v>0.7906570816031738</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3697364001410003</v>
+        <v>0.0312690549469319</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Consumer Defensive_w</t>
+          <t>Communication Services_w</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>const</t>
+          <t>Real Estate_logp</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.936047948050522</v>
+        <v>0.7906570816031738</v>
       </c>
       <c r="D24" t="n">
-        <v>8.446227931776678e-14</v>
+        <v>0.2372252922004072</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Consumer Defensive_w</t>
+          <t>Communication Services_w</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Communication Services_logp</t>
+          <t>Technology_logp</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.936047948050522</v>
+        <v>0.7906570816031738</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8648272651873304</v>
+        <v>6.0779494450165e-13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Consumer Defensive_w</t>
+          <t>Communication Services_w</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Consumer Cyclical_logp</t>
+          <t>Utilities_logp</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.936047948050522</v>
+        <v>0.7906570816031738</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3756271463867064</v>
+        <v>0.3641780527333305</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Consumer Defensive_w</t>
+          <t>Communication Services_w</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Consumer Defensive_logp</t>
+          <t>log_real_income</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.936047948050522</v>
+        <v>0.7906570816031738</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0009683279126339</v>
+        <v>0.000162253397999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Consumer Defensive_w</t>
+          <t>Consumer Cyclical_w</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Energy_logp</t>
+          <t>const</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.936047948050522</v>
+        <v>0.8856936811598749</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7848261920593737</v>
+        <v>0.1067159326470008</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Consumer Defensive_w</t>
+          <t>Consumer Cyclical_w</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Financial Services_logp</t>
+          <t>Basic Materials_logp</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.936047948050522</v>
+        <v>0.8856936811598749</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6169550203377943</v>
+        <v>0.8277372817246025</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Consumer Defensive_w</t>
+          <t>Consumer Cyclical_w</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Healthcare_logp</t>
+          <t>Communication Services_logp</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.936047948050522</v>
+        <v>0.8856936811598749</v>
       </c>
       <c r="D30" t="n">
-        <v>1.138682073946003e-06</v>
+        <v>0.8395387864538115</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Consumer Defensive_w</t>
+          <t>Consumer Cyclical_w</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Industrials_logp</t>
+          <t>Consumer Cyclical_logp</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.936047948050522</v>
+        <v>0.8856936811598749</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3346911216970873</v>
+        <v>0.9800096200606708</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Consumer Defensive_w</t>
+          <t>Consumer Cyclical_w</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Technology_logp</t>
+          <t>Consumer Defensive_logp</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.936047948050522</v>
+        <v>0.8856936811598749</v>
       </c>
       <c r="D32" t="n">
-        <v>7.549493301816088e-05</v>
+        <v>0.7208417967917762</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Consumer Defensive_w</t>
+          <t>Consumer Cyclical_w</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Utilities_logp</t>
+          <t>Energy_logp</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.936047948050522</v>
+        <v>0.8856936811598749</v>
       </c>
       <c r="D33" t="n">
-        <v>0.6849632273236506</v>
+        <v>2.144314632865566e-08</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Consumer Defensive_w</t>
+          <t>Consumer Cyclical_w</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>log_real_income</t>
+          <t>Financial Services_logp</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.936047948050522</v>
+        <v>0.8856936811598749</v>
       </c>
       <c r="D34" t="n">
-        <v>7.516730381518133e-10</v>
+        <v>0.0005403772746672</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Energy_w</t>
+          <t>Consumer Cyclical_w</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>const</t>
+          <t>Healthcare_logp</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.7692661115116314</v>
+        <v>0.8856936811598749</v>
       </c>
       <c r="D35" t="n">
-        <v>3.579798072927002e-08</v>
+        <v>0.185003230793901</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Energy_w</t>
+          <t>Consumer Cyclical_w</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Communication Services_logp</t>
+          <t>Industrials_logp</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.7692661115116314</v>
+        <v>0.8856936811598749</v>
       </c>
       <c r="D36" t="n">
-        <v>0.5035599197351985</v>
+        <v>0.3147781674184031</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Energy_w</t>
+          <t>Consumer Cyclical_w</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Consumer Cyclical_logp</t>
+          <t>Real Estate_logp</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.7692661115116314</v>
+        <v>0.8856936811598749</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0011086952589787</v>
+        <v>0.0005011400569085</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Energy_w</t>
+          <t>Consumer Cyclical_w</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Consumer Defensive_logp</t>
+          <t>Technology_logp</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.7692661115116314</v>
+        <v>0.8856936811598749</v>
       </c>
       <c r="D38" t="n">
-        <v>1.18706309787027e-05</v>
+        <v>8.766417426536565e-05</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Energy_w</t>
+          <t>Consumer Cyclical_w</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Energy_logp</t>
+          <t>Utilities_logp</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.7692661115116314</v>
+        <v>0.8856936811598749</v>
       </c>
       <c r="D39" t="n">
-        <v>1.726559170884202e-06</v>
+        <v>0.210701789289903</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Energy_w</t>
+          <t>Consumer Cyclical_w</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Financial Services_logp</t>
+          <t>log_real_income</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.7692661115116314</v>
+        <v>0.8856936811598749</v>
       </c>
       <c r="D40" t="n">
-        <v>6.286244282859171e-06</v>
+        <v>0.7118288915465536</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Energy_w</t>
+          <t>Consumer Defensive_w</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Healthcare_logp</t>
+          <t>const</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.7692661115116314</v>
+        <v>0.9140537982890016</v>
       </c>
       <c r="D41" t="n">
-        <v>0.8119646828188634</v>
+        <v>4.159431758777523e-07</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Energy_w</t>
+          <t>Consumer Defensive_w</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Industrials_logp</t>
+          <t>Basic Materials_logp</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.7692661115116314</v>
+        <v>0.9140537982890016</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0058205235944244</v>
+        <v>0.0479418839476345</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Energy_w</t>
+          <t>Consumer Defensive_w</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Technology_logp</t>
+          <t>Communication Services_logp</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.7692661115116314</v>
+        <v>0.9140537982890016</v>
       </c>
       <c r="D43" t="n">
-        <v>4.078389221948665e-06</v>
+        <v>0.1617778335934516</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Energy_w</t>
+          <t>Consumer Defensive_w</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Utilities_logp</t>
+          <t>Consumer Cyclical_logp</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.7692661115116314</v>
+        <v>0.9140537982890016</v>
       </c>
       <c r="D44" t="n">
-        <v>5.347435199670433e-08</v>
+        <v>0.1370003405571238</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Energy_w</t>
+          <t>Consumer Defensive_w</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>log_real_income</t>
+          <t>Consumer Defensive_logp</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.7692661115116314</v>
+        <v>0.9140537982890016</v>
       </c>
       <c r="D45" t="n">
-        <v>0.6498736072551656</v>
+        <v>0.0014459314569371</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Financial Services_w</t>
+          <t>Consumer Defensive_w</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>const</t>
+          <t>Energy_logp</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.8011839164645616</v>
+        <v>0.9140537982890016</v>
       </c>
       <c r="D46" t="n">
-        <v>2.778180932888265e-05</v>
+        <v>0.5808269036789796</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Financial Services_w</t>
+          <t>Consumer Defensive_w</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Communication Services_logp</t>
+          <t>Financial Services_logp</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.8011839164645616</v>
+        <v>0.9140537982890016</v>
       </c>
       <c r="D47" t="n">
-        <v>0.7792715713063136</v>
+        <v>0.6582874586398484</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Financial Services_w</t>
+          <t>Consumer Defensive_w</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Consumer Cyclical_logp</t>
+          <t>Healthcare_logp</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.8011839164645616</v>
+        <v>0.9140537982890016</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0021672607145621</v>
+        <v>0.0005923311135460001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Financial Services_w</t>
+          <t>Consumer Defensive_w</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Consumer Defensive_logp</t>
+          <t>Industrials_logp</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.8011839164645616</v>
+        <v>0.9140537982890016</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0032184550562067</v>
+        <v>0.7386485818780182</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Financial Services_w</t>
+          <t>Consumer Defensive_w</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Energy_logp</t>
+          <t>Real Estate_logp</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.8011839164645616</v>
+        <v>0.9140537982890016</v>
       </c>
       <c r="D50" t="n">
-        <v>0.2092005368491181</v>
+        <v>0.1872408444352502</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Financial Services_w</t>
+          <t>Consumer Defensive_w</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Financial Services_logp</t>
+          <t>Technology_logp</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.8011839164645616</v>
+        <v>0.9140537982890016</v>
       </c>
       <c r="D51" t="n">
-        <v>0.1430668240002326</v>
+        <v>0.4056926365131629</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Financial Services_w</t>
+          <t>Consumer Defensive_w</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Healthcare_logp</t>
+          <t>Utilities_logp</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.8011839164645616</v>
+        <v>0.9140537982890016</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0015586035159885</v>
+        <v>0.0846574472799481</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Financial Services_w</t>
+          <t>Consumer Defensive_w</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Industrials_logp</t>
+          <t>log_real_income</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.8011839164645616</v>
+        <v>0.9140537982890016</v>
       </c>
       <c r="D53" t="n">
-        <v>0.1607692043714618</v>
+        <v>0.0009258107264843</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Financial Services_w</t>
+          <t>Energy_w</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Technology_logp</t>
+          <t>const</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.8011839164645616</v>
+        <v>0.7764479654670438</v>
       </c>
       <c r="D54" t="n">
-        <v>1.199571711049417e-12</v>
+        <v>0.0008671047476147</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Financial Services_w</t>
+          <t>Energy_w</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Utilities_logp</t>
+          <t>Basic Materials_logp</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.8011839164645616</v>
+        <v>0.7764479654670438</v>
       </c>
       <c r="D55" t="n">
-        <v>0.8290018055971154</v>
+        <v>0.6457290571311772</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Financial Services_w</t>
+          <t>Energy_w</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>log_real_income</t>
+          <t>Communication Services_logp</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.8011839164645616</v>
+        <v>0.7764479654670438</v>
       </c>
       <c r="D56" t="n">
-        <v>2.309497872306979e-06</v>
+        <v>0.5463787468779139</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Healthcare_w</t>
+          <t>Energy_w</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>const</t>
+          <t>Consumer Cyclical_logp</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.7399531901570706</v>
+        <v>0.7764479654670438</v>
       </c>
       <c r="D57" t="n">
-        <v>0.9692356746686224</v>
+        <v>0.0004800584522747</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Healthcare_w</t>
+          <t>Energy_w</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Communication Services_logp</t>
+          <t>Consumer Defensive_logp</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.7399531901570706</v>
+        <v>0.7764479654670438</v>
       </c>
       <c r="D58" t="n">
-        <v>0.0063669856588632</v>
+        <v>2.830556891879255e-06</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Healthcare_w</t>
+          <t>Energy_w</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Consumer Cyclical_logp</t>
+          <t>Energy_logp</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.7399531901570706</v>
+        <v>0.7764479654670438</v>
       </c>
       <c r="D59" t="n">
-        <v>0.0060835901615442</v>
+        <v>8.291228866203746e-08</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Healthcare_w</t>
+          <t>Energy_w</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Consumer Defensive_logp</t>
+          <t>Financial Services_logp</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.7399531901570706</v>
+        <v>0.7764479654670438</v>
       </c>
       <c r="D60" t="n">
-        <v>0.7230227146425048</v>
+        <v>0.0001884113207303</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Healthcare_w</t>
+          <t>Energy_w</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Energy_logp</t>
+          <t>Healthcare_logp</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.7399531901570706</v>
+        <v>0.7764479654670438</v>
       </c>
       <c r="D61" t="n">
-        <v>0.4817161133590605</v>
+        <v>0.275700395116781</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Healthcare_w</t>
+          <t>Energy_w</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Financial Services_logp</t>
+          <t>Industrials_logp</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.7399531901570706</v>
+        <v>0.7764479654670438</v>
       </c>
       <c r="D62" t="n">
-        <v>0.0007413133109011</v>
+        <v>0.009550794138123099</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Healthcare_w</t>
+          <t>Energy_w</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Healthcare_logp</t>
+          <t>Real Estate_logp</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.7399531901570706</v>
+        <v>0.7764479654670438</v>
       </c>
       <c r="D63" t="n">
-        <v>0.040839372286097</v>
+        <v>0.09405296718806069</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Healthcare_w</t>
+          <t>Energy_w</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Industrials_logp</t>
+          <t>Technology_logp</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.7399531901570706</v>
+        <v>0.7764479654670438</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0993611728832525</v>
+        <v>2.062931909364904e-07</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Healthcare_w</t>
+          <t>Energy_w</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Technology_logp</t>
+          <t>Utilities_logp</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.7399531901570706</v>
+        <v>0.7764479654670438</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0216746358389887</v>
+        <v>0.11040210276406</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Healthcare_w</t>
+          <t>Energy_w</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Utilities_logp</t>
+          <t>log_real_income</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.7399531901570706</v>
+        <v>0.7764479654670438</v>
       </c>
       <c r="D66" t="n">
-        <v>1.194798607283327e-05</v>
+        <v>0.096926317774978</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Healthcare_w</t>
+          <t>Financial Services_w</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>log_real_income</t>
+          <t>const</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.7399531901570706</v>
+        <v>0.6250595072412953</v>
       </c>
       <c r="D67" t="n">
-        <v>0.474075724261311</v>
+        <v>0.3305503135975175</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Industrials_w</t>
+          <t>Financial Services_w</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>const</t>
+          <t>Basic Materials_logp</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.9033637582537216</v>
+        <v>0.6250595072412953</v>
       </c>
       <c r="D68" t="n">
-        <v>0.009409140107393899</v>
+        <v>0.1784353093454304</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Industrials_w</t>
+          <t>Financial Services_w</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1668,16 +1668,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.9033637582537216</v>
+        <v>0.6250595072412953</v>
       </c>
       <c r="D69" t="n">
-        <v>0.019149259040907</v>
+        <v>0.8856024957553547</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Industrials_w</t>
+          <t>Financial Services_w</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1686,16 +1686,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.9033637582537216</v>
+        <v>0.6250595072412953</v>
       </c>
       <c r="D70" t="n">
-        <v>0.1346782110806934</v>
+        <v>0.0429932555232042</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Industrials_w</t>
+          <t>Financial Services_w</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1704,16 +1704,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.9033637582537216</v>
+        <v>0.6250595072412953</v>
       </c>
       <c r="D71" t="n">
-        <v>0.1396349034653567</v>
+        <v>0.0026880352279896</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Industrials_w</t>
+          <t>Financial Services_w</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1722,16 +1722,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.9033637582537216</v>
+        <v>0.6250595072412953</v>
       </c>
       <c r="D72" t="n">
-        <v>0.0433573017263502</v>
+        <v>0.171262701643447</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Industrials_w</t>
+          <t>Financial Services_w</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1740,16 +1740,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.9033637582537216</v>
+        <v>0.6250595072412953</v>
       </c>
       <c r="D73" t="n">
-        <v>0.0009157736056875</v>
+        <v>0.4932403712732812</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Industrials_w</t>
+          <t>Financial Services_w</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1758,16 +1758,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.9033637582537216</v>
+        <v>0.6250595072412953</v>
       </c>
       <c r="D74" t="n">
-        <v>0.9599843792873192</v>
+        <v>0.5748193594722264</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Industrials_w</t>
+          <t>Financial Services_w</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1776,262 +1776,1018 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.9033637582537216</v>
+        <v>0.6250595072412953</v>
       </c>
       <c r="D75" t="n">
-        <v>0.2496299721164169</v>
+        <v>0.0398031603447727</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Industrials_w</t>
+          <t>Financial Services_w</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Technology_logp</t>
+          <t>Real Estate_logp</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.9033637582537216</v>
+        <v>0.6250595072412953</v>
       </c>
       <c r="D76" t="n">
-        <v>0.0658547751319437</v>
+        <v>0.279872289500388</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Industrials_w</t>
+          <t>Financial Services_w</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Utilities_logp</t>
+          <t>Technology_logp</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.9033637582537216</v>
+        <v>0.6250595072412953</v>
       </c>
       <c r="D77" t="n">
-        <v>0.4723751625452049</v>
+        <v>0.0005303974594857</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Industrials_w</t>
+          <t>Financial Services_w</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>log_real_income</t>
+          <t>Utilities_logp</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.9033637582537216</v>
+        <v>0.6250595072412953</v>
       </c>
       <c r="D78" t="n">
-        <v>0.0734083029060168</v>
+        <v>0.1019379460410076</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Technology_w</t>
+          <t>Financial Services_w</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>const</t>
+          <t>log_real_income</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.9243212087172136</v>
+        <v>0.6250595072412953</v>
       </c>
       <c r="D79" t="n">
-        <v>0.08887714807359599</v>
+        <v>0.0453223403466859</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Technology_w</t>
+          <t>Healthcare_w</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Communication Services_logp</t>
+          <t>const</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.9243212087172136</v>
+        <v>0.7287321269585409</v>
       </c>
       <c r="D80" t="n">
-        <v>0.1998218025500469</v>
+        <v>0.5269231045215246</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Technology_w</t>
+          <t>Healthcare_w</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Consumer Cyclical_logp</t>
+          <t>Basic Materials_logp</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0.9243212087172136</v>
+        <v>0.7287321269585409</v>
       </c>
       <c r="D81" t="n">
-        <v>0.8711170514665615</v>
+        <v>1.593780879486466e-05</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Technology_w</t>
+          <t>Healthcare_w</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Consumer Defensive_logp</t>
+          <t>Communication Services_logp</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>0.9243212087172136</v>
+        <v>0.7287321269585409</v>
       </c>
       <c r="D82" t="n">
-        <v>0.0997275247280732</v>
+        <v>0.001442207267089</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Technology_w</t>
+          <t>Healthcare_w</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Energy_logp</t>
+          <t>Consumer Cyclical_logp</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>0.9243212087172136</v>
+        <v>0.7287321269585409</v>
       </c>
       <c r="D83" t="n">
-        <v>0.2012463497983508</v>
+        <v>0.0054642818935383</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Technology_w</t>
+          <t>Healthcare_w</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Financial Services_logp</t>
+          <t>Consumer Defensive_logp</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0.9243212087172136</v>
+        <v>0.7287321269585409</v>
       </c>
       <c r="D84" t="n">
-        <v>0.5147174693093843</v>
+        <v>0.6039441955356102</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Technology_w</t>
+          <t>Healthcare_w</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Healthcare_logp</t>
+          <t>Energy_logp</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0.9243212087172136</v>
+        <v>0.7287321269585409</v>
       </c>
       <c r="D85" t="n">
-        <v>0.015531052370263</v>
+        <v>0.0025112470597092</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Technology_w</t>
+          <t>Healthcare_w</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Industrials_logp</t>
+          <t>Financial Services_logp</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>0.9243212087172136</v>
+        <v>0.7287321269585409</v>
       </c>
       <c r="D86" t="n">
-        <v>0.5865174764957586</v>
+        <v>0.0024725709085343</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Technology_w</t>
+          <t>Healthcare_w</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Technology_logp</t>
+          <t>Healthcare_logp</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>0.9243212087172136</v>
+        <v>0.7287321269585409</v>
       </c>
       <c r="D87" t="n">
-        <v>2.44551443121704e-05</v>
+        <v>0.6785771158693008</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Technology_w</t>
+          <t>Healthcare_w</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Utilities_logp</t>
+          <t>Industrials_logp</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>0.9243212087172136</v>
+        <v>0.7287321269585409</v>
       </c>
       <c r="D88" t="n">
-        <v>0.2992979339565306</v>
+        <v>0.8849305363039752</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>Healthcare_w</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Real Estate_logp</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>0.7287321269585409</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.4645965184655611</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Healthcare_w</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Technology_logp</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>0.7287321269585409</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0.965727602357856</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Healthcare_w</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Utilities_logp</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>0.7287321269585409</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0.1613194589759322</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Healthcare_w</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>log_real_income</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>0.7287321269585409</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0.3402127230299276</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Industrials_w</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>const</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>0.5112001288705881</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.1895840595640315</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Industrials_w</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Basic Materials_logp</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>0.5112001288705881</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0.0491657018912059</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Industrials_w</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Communication Services_logp</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>0.5112001288705881</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0.0529759285166738</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Industrials_w</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical_logp</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>0.5112001288705881</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.0887208892909498</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Industrials_w</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Consumer Defensive_logp</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>0.5112001288705881</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.8409596604196974</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Industrials_w</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Energy_logp</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>0.5112001288705881</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0.6890782058845764</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Industrials_w</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Financial Services_logp</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>0.5112001288705881</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0.3755152451646171</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Industrials_w</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Healthcare_logp</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>0.5112001288705881</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.7131245992645081</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Industrials_w</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Industrials_logp</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>0.5112001288705881</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0.1151973307047488</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Industrials_w</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Real Estate_logp</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>0.5112001288705881</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0.0541625808719982</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Industrials_w</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Technology_logp</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>0.5112001288705881</v>
+      </c>
+      <c r="D103" t="n">
+        <v>6.186081696226109e-06</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Industrials_w</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Utilities_logp</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>0.5112001288705881</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0.0008316866539635</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Industrials_w</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>log_real_income</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>0.5112001288705881</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0.7608464502296718</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Real Estate_w</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>const</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>0.7426524614661432</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0.0029809646247917</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Real Estate_w</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Basic Materials_logp</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>0.7426524614661432</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0.375644134037575</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Real Estate_w</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Communication Services_logp</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>0.7426524614661432</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0.2325517501700331</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Real Estate_w</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical_logp</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>0.7426524614661432</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0.7742065910533593</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Real Estate_w</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Consumer Defensive_logp</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>0.7426524614661432</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0.0165250987085094</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Real Estate_w</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Energy_logp</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>0.7426524614661432</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0.0005160330100704</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Real Estate_w</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Financial Services_logp</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>0.7426524614661432</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0.7577257969339768</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Real Estate_w</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Healthcare_logp</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>0.7426524614661432</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0.1024376146457047</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Real Estate_w</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Industrials_logp</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>0.7426524614661432</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0.6121297949564928</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Real Estate_w</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Real Estate_logp</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>0.7426524614661432</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0.5087219333095339</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Real Estate_w</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Technology_logp</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>0.7426524614661432</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0.982852848981134</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Real Estate_w</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Utilities_logp</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7426524614661432</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.4154776659421335</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Real Estate_w</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>log_real_income</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7426524614661432</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.4650385903041584</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
           <t>Technology_w</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>const</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>0.9140073781111462</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.2323585871014064</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Technology_w</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Basic Materials_logp</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>0.9140073781111462</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.0569695550551597</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Technology_w</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Communication Services_logp</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>0.9140073781111462</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.1206595919809442</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Technology_w</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical_logp</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>0.9140073781111462</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.8941802138213529</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Technology_w</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Consumer Defensive_logp</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>0.9140073781111462</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.1328540994841207</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Technology_w</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Energy_logp</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>0.9140073781111462</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.1902520000157522</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Technology_w</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Financial Services_logp</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9140073781111462</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.2853915478464061</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Technology_w</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Healthcare_logp</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>0.9140073781111462</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.0465953220360312</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Technology_w</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Industrials_logp</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>0.9140073781111462</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.1306527007606008</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Technology_w</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Real Estate_logp</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>0.9140073781111462</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.1362138593009111</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Technology_w</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Technology_logp</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>0.9140073781111462</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.0001298517086949</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Technology_w</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Utilities_logp</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>0.9140073781111462</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.5268608069402202</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Technology_w</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
         <is>
           <t>log_real_income</t>
         </is>
       </c>
-      <c r="C89" t="n">
-        <v>0.9243212087172136</v>
-      </c>
-      <c r="D89" t="n">
-        <v>0.2223010345079089</v>
+      <c r="C131" t="n">
+        <v>0.9140073781111462</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.1063304269659734</v>
       </c>
     </row>
   </sheetData>
